--- a/rollforever/Assets/Excels/SkillConfig.xlsx
+++ b/rollforever/Assets/Excels/SkillConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\rollforever\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B1B302-0BA4-461D-BCC8-52D88FFD9E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93767CD-FC06-4E2C-8B9E-F02B251AC554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9892" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4250" yWindow="1270" windowWidth="14400" windowHeight="8210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="baseData" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <t>level</t>
   </si>
   <si>
-    <t>skillId</t>
+    <t>skill_id</t>
   </si>
 </sst>
 </file>
@@ -374,27 +374,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.4609375" customWidth="1"/>
-    <col min="2" max="2" width="11.765625" customWidth="1"/>
-    <col min="3" max="3" width="10.84375" customWidth="1"/>
-    <col min="4" max="4" width="14.61328125" customWidth="1"/>
-    <col min="5" max="5" width="19.3828125" customWidth="1"/>
-    <col min="6" max="6" width="21.4609375" customWidth="1"/>
-    <col min="7" max="7" width="19.921875" customWidth="1"/>
-    <col min="8" max="8" width="18.69140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.23046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.4609375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.84375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.61328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.84375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.3828125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" customWidth="1"/>
+    <col min="4" max="4" width="14.6328125" customWidth="1"/>
+    <col min="5" max="5" width="19.36328125" customWidth="1"/>
+    <col min="6" max="6" width="21.453125" customWidth="1"/>
+    <col min="7" max="7" width="19.90625" customWidth="1"/>
+    <col min="8" max="8" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="16.3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -426,7 +426,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="b">
         <v>0</v>
       </c>
@@ -450,7 +450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" t="b">
         <v>0</v>
       </c>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="b">
         <v>1</v>
       </c>
